--- a/outputs/50811.xlsx
+++ b/outputs/50811.xlsx
@@ -374,115 +374,115 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1353,7 +1353,7 @@
         <v>30</v>
       </c>
       <c r="D21" s="25" t="n">
-        <f aca="false">INDEX($H$5:$T$12, MATCH($C21,$C$5:$C$12,0), (MATCH($B21, INDEX($F$5:$R$12, MATCH($C21,$C$5:$C$12,0),0),0)-1)*3+1)</f>
+        <f aca="false">INDEX($F$5:$T$12,MATCH(C21,$C$5:$C$12,0),MATCH(B21,INDEX($F$5:$T$12,MATCH(C21,$C$5:$C$12,0),0),0)+2)</f>
         <v>0.06</v>
       </c>
       <c r="F21" s="2"/>
@@ -1369,9 +1369,9 @@
       <c r="C22" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="27" t="e">
-        <f aca="false">INDEX($H$5:$T$12, MATCH($C22,$C$5:$C$12,0), (MATCH($B22, INDEX($F$5:$R$12, MATCH($C22,$C$5:$C$12,0),0),0)-1)*3+1)</f>
-        <v>#REF!</v>
+      <c r="D22" s="27" t="n">
+        <f aca="false">INDEX($F$5:$T$12,MATCH(C22,$C$5:$C$12,0),MATCH(B22,INDEX($F$5:$T$12,MATCH(C22,$C$5:$C$12,0),0),0)+2)</f>
+        <v>0.1</v>
       </c>
       <c r="F22" s="2"/>
       <c r="I22" s="2"/>
@@ -1386,9 +1386,9 @@
       <c r="C23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="27" t="e">
-        <f aca="false">INDEX($H$5:$T$12, MATCH($C23,$C$5:$C$12,0), (MATCH($B23, INDEX($F$5:$R$12, MATCH($C23,$C$5:$C$12,0),0),0)-1)*3+1)</f>
-        <v>#REF!</v>
+      <c r="D23" s="27" t="n">
+        <f aca="false">INDEX($F$5:$T$12,MATCH(C23,$C$5:$C$12,0),MATCH(B23,INDEX($F$5:$T$12,MATCH(C23,$C$5:$C$12,0),0),0)+2)</f>
+        <v>0.09</v>
       </c>
       <c r="F23" s="2"/>
       <c r="I23" s="2"/>
